--- a/products/Resource Histogram Starter.xlsx
+++ b/products/Resource Histogram Starter.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Histogram" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Histogram'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="mmm d, yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +90,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0033415C"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -143,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,6 +201,7 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -719,6 +728,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0014213D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -802,10 +812,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1318,14 +1329,24 @@
       </c>
       <c r="O17" s="20" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>CPM Toolkit  |  Resource Histogram Starter  |  v1.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A4:O4"/>
+  <mergeCells count="5">
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A4:O4"/>
     <mergeCell ref="I1:J1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/products/Resource Histogram Starter.xlsx
+++ b/products/Resource Histogram Starter.xlsx
@@ -980,11 +980,11 @@
         <v>0</v>
       </c>
       <c r="N5" s="11">
-        <f>MAX(B5:M5)</f>
+        <f>IF(COUNT(B5:M5)=0,"",MAX(B5:M5))</f>
         <v/>
       </c>
       <c r="O5" s="12">
-        <f>AVERAGE(B5:M5)</f>
+        <f>IF(COUNT(B5:M5)=0,"",AVERAGE(B5:M5))</f>
         <v/>
       </c>
     </row>
@@ -1031,11 +1031,11 @@
         <v>2</v>
       </c>
       <c r="N6" s="11">
-        <f>MAX(B6:M6)</f>
+        <f>IF(COUNT(B6:M6)=0,"",MAX(B6:M6))</f>
         <v/>
       </c>
       <c r="O6" s="12">
-        <f>AVERAGE(B6:M6)</f>
+        <f>IF(COUNT(B6:M6)=0,"",AVERAGE(B6:M6))</f>
         <v/>
       </c>
     </row>
@@ -1054,11 +1054,11 @@
       <c r="L7" s="14" t="n"/>
       <c r="M7" s="14" t="n"/>
       <c r="N7" s="11">
-        <f>MAX(B7:M7)</f>
+        <f>IF(COUNT(B7:M7)=0,"",MAX(B7:M7))</f>
         <v/>
       </c>
       <c r="O7" s="12">
-        <f>AVERAGE(B7:M7)</f>
+        <f>IF(COUNT(B7:M7)=0,"",AVERAGE(B7:M7))</f>
         <v/>
       </c>
     </row>
@@ -1077,11 +1077,11 @@
       <c r="L8" s="16" t="n"/>
       <c r="M8" s="16" t="n"/>
       <c r="N8" s="17">
-        <f>MAX(B8:M8)</f>
+        <f>IF(COUNT(B8:M8)=0,"",MAX(B8:M8))</f>
         <v/>
       </c>
       <c r="O8" s="18">
-        <f>AVERAGE(B8:M8)</f>
+        <f>IF(COUNT(B8:M8)=0,"",AVERAGE(B8:M8))</f>
         <v/>
       </c>
     </row>
@@ -1100,11 +1100,11 @@
       <c r="L9" s="14" t="n"/>
       <c r="M9" s="14" t="n"/>
       <c r="N9" s="11">
-        <f>MAX(B9:M9)</f>
+        <f>IF(COUNT(B9:M9)=0,"",MAX(B9:M9))</f>
         <v/>
       </c>
       <c r="O9" s="12">
-        <f>AVERAGE(B9:M9)</f>
+        <f>IF(COUNT(B9:M9)=0,"",AVERAGE(B9:M9))</f>
         <v/>
       </c>
     </row>
@@ -1123,11 +1123,11 @@
       <c r="L10" s="16" t="n"/>
       <c r="M10" s="16" t="n"/>
       <c r="N10" s="17">
-        <f>MAX(B10:M10)</f>
+        <f>IF(COUNT(B10:M10)=0,"",MAX(B10:M10))</f>
         <v/>
       </c>
       <c r="O10" s="18">
-        <f>AVERAGE(B10:M10)</f>
+        <f>IF(COUNT(B10:M10)=0,"",AVERAGE(B10:M10))</f>
         <v/>
       </c>
     </row>
@@ -1146,11 +1146,11 @@
       <c r="L11" s="14" t="n"/>
       <c r="M11" s="14" t="n"/>
       <c r="N11" s="11">
-        <f>MAX(B11:M11)</f>
+        <f>IF(COUNT(B11:M11)=0,"",MAX(B11:M11))</f>
         <v/>
       </c>
       <c r="O11" s="12">
-        <f>AVERAGE(B11:M11)</f>
+        <f>IF(COUNT(B11:M11)=0,"",AVERAGE(B11:M11))</f>
         <v/>
       </c>
     </row>
@@ -1169,11 +1169,11 @@
       <c r="L12" s="16" t="n"/>
       <c r="M12" s="16" t="n"/>
       <c r="N12" s="17">
-        <f>MAX(B12:M12)</f>
+        <f>IF(COUNT(B12:M12)=0,"",MAX(B12:M12))</f>
         <v/>
       </c>
       <c r="O12" s="18">
-        <f>AVERAGE(B12:M12)</f>
+        <f>IF(COUNT(B12:M12)=0,"",AVERAGE(B12:M12))</f>
         <v/>
       </c>
     </row>
@@ -1192,11 +1192,11 @@
       <c r="L13" s="14" t="n"/>
       <c r="M13" s="14" t="n"/>
       <c r="N13" s="11">
-        <f>MAX(B13:M13)</f>
+        <f>IF(COUNT(B13:M13)=0,"",MAX(B13:M13))</f>
         <v/>
       </c>
       <c r="O13" s="12">
-        <f>AVERAGE(B13:M13)</f>
+        <f>IF(COUNT(B13:M13)=0,"",AVERAGE(B13:M13))</f>
         <v/>
       </c>
     </row>
@@ -1215,11 +1215,11 @@
       <c r="L14" s="16" t="n"/>
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="17">
-        <f>MAX(B14:M14)</f>
+        <f>IF(COUNT(B14:M14)=0,"",MAX(B14:M14))</f>
         <v/>
       </c>
       <c r="O14" s="18">
-        <f>AVERAGE(B14:M14)</f>
+        <f>IF(COUNT(B14:M14)=0,"",AVERAGE(B14:M14))</f>
         <v/>
       </c>
     </row>
@@ -1238,11 +1238,11 @@
       <c r="L15" s="14" t="n"/>
       <c r="M15" s="14" t="n"/>
       <c r="N15" s="11">
-        <f>MAX(B15:M15)</f>
+        <f>IF(COUNT(B15:M15)=0,"",MAX(B15:M15))</f>
         <v/>
       </c>
       <c r="O15" s="12">
-        <f>AVERAGE(B15:M15)</f>
+        <f>IF(COUNT(B15:M15)=0,"",AVERAGE(B15:M15))</f>
         <v/>
       </c>
     </row>
@@ -1261,11 +1261,11 @@
       <c r="L16" s="16" t="n"/>
       <c r="M16" s="16" t="n"/>
       <c r="N16" s="17">
-        <f>MAX(B16:M16)</f>
+        <f>IF(COUNT(B16:M16)=0,"",MAX(B16:M16))</f>
         <v/>
       </c>
       <c r="O16" s="18">
-        <f>AVERAGE(B16:M16)</f>
+        <f>IF(COUNT(B16:M16)=0,"",AVERAGE(B16:M16))</f>
         <v/>
       </c>
     </row>
